--- a/Launcher DB 251.xlsx
+++ b/Launcher DB 251.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdepaor2\Desktop\ORLA_Lander_Mission_Architecture\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2B9FDE-B9D9-4FE4-A6DE-5A5038FACF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4619C257-A6DA-4DF4-8E3E-1D64AF345E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{69C8745A-9C92-45EB-911F-DC35D6424AAB}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{69C8745A-9C92-45EB-911F-DC35D6424AAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -207,8 +207,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -604,7 +602,7 @@
         <v>63800</v>
       </c>
       <c r="D2" s="3">
-        <f>B2/C2</f>
+        <f t="shared" ref="D2:D10" si="0">B2/C2</f>
         <v>2351.0971786833857</v>
       </c>
       <c r="E2" s="3">
@@ -636,14 +634,14 @@
         <v>18831</v>
       </c>
       <c r="D3" s="6">
-        <f>B3/C3</f>
+        <f t="shared" si="0"/>
         <v>3876.5864797408531</v>
       </c>
       <c r="E3" s="6">
         <v>2462</v>
       </c>
       <c r="F3" s="2">
-        <f t="shared" ref="F3:F11" si="0">0.5*(C3+E3)*9500^2</f>
+        <f t="shared" ref="F3:F10" si="1">0.5*(C3+E3)*9500^2</f>
         <v>960846625000</v>
       </c>
       <c r="G3" s="7"/>
@@ -651,10 +649,10 @@
         <v>8900</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I11" si="1">2*F3/(13400^2)-E3</f>
+        <f t="shared" ref="I3:I10" si="2">2*F3/(13400^2)-E3</f>
         <v>8240.2346290933401</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="7" t="s">
         <v>17</v>
       </c>
     </row>
@@ -669,24 +667,24 @@
         <v>21650</v>
       </c>
       <c r="D4" s="3">
-        <f>B4/C4</f>
+        <f t="shared" si="0"/>
         <v>5311.778290993072</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>3500</v>
       </c>
       <c r="F4" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1134893750000</v>
       </c>
       <c r="H4" s="3">
         <v>11500</v>
       </c>
       <c r="I4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9140.8303631098242</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -701,14 +699,14 @@
         <v>22800</v>
       </c>
       <c r="D5" s="6">
-        <f>B5/C5</f>
+        <f t="shared" si="0"/>
         <v>2938.5964912280701</v>
       </c>
       <c r="E5" s="6">
         <v>3900</v>
       </c>
       <c r="F5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1204837500000</v>
       </c>
       <c r="G5" s="7"/>
@@ -716,7 +714,7 @@
         <v>8300</v>
       </c>
       <c r="I5" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9519.8875027845843</v>
       </c>
       <c r="J5" s="7" t="s">
@@ -734,22 +732,22 @@
         <v>95000</v>
       </c>
       <c r="D6" s="3">
-        <f>B6/C6</f>
+        <f t="shared" si="0"/>
         <v>21052.63157894737</v>
       </c>
       <c r="E6" s="3">
         <v>3490</v>
       </c>
       <c r="F6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4444361250000</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>46012.798507462685</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="9" t="s">
         <v>24</v>
       </c>
     </row>
@@ -764,14 +762,14 @@
         <v>3300</v>
       </c>
       <c r="D7" s="6">
-        <f>B7/C7</f>
+        <f t="shared" si="0"/>
         <v>11212.121212121212</v>
       </c>
       <c r="E7" s="6">
         <v>698</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>180409750000</v>
       </c>
       <c r="G7" s="5">
@@ -779,7 +777,7 @@
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1311.4648028514146</v>
       </c>
       <c r="J7" s="7" t="s">
@@ -797,16 +795,16 @@
         <v>220</v>
       </c>
       <c r="D8" s="3">
-        <f>B8/C8</f>
+        <f t="shared" si="0"/>
         <v>24090.909090909092</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="10"/>
       <c r="F8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9927500000</v>
       </c>
       <c r="H8" s="3"/>
-      <c r="I8" s="12"/>
+      <c r="I8" s="10"/>
       <c r="J8" t="s">
         <v>10</v>
       </c>
@@ -822,17 +820,17 @@
         <v>8200</v>
       </c>
       <c r="D9" s="6">
-        <f>B9/C9</f>
+        <f t="shared" si="0"/>
         <v>10365.853658536585</v>
       </c>
-      <c r="E9" s="12"/>
+      <c r="E9" s="10"/>
       <c r="F9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>370025000000</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="6"/>
-      <c r="I9" s="12"/>
+      <c r="I9" s="10"/>
       <c r="J9" s="8" t="s">
         <v>12</v>
       </c>
@@ -848,18 +846,18 @@
         <v>7430</v>
       </c>
       <c r="D10" s="3">
-        <f>B10/C10</f>
+        <f t="shared" si="0"/>
         <v>6527.5908479138625</v>
       </c>
       <c r="E10" s="3">
         <v>2355</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>441548125000</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2563.1123301403431</v>
       </c>
       <c r="J10" t="s">
